--- a/MannualTestingAssessment/TC_Purple_29_JUNE_Shahbaz_Ahmad.xlsx
+++ b/MannualTestingAssessment/TC_Purple_29_JUNE_Shahbaz_Ahmad.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\307424\Documents\QA Training\Assessment\FirstIntrimTest\SDET\MannualTestingAssessment\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10F164B8-316B-4835-9962-C1E177018F65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3FFFC86-1B44-4EBC-9CEC-4B8BB5559187}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{CC8C8E7E-B3D0-4506-A3F4-91518E10C04F}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="83">
   <si>
     <t>testcase Title</t>
   </si>
@@ -131,6 +131,12 @@
     <t>Images, price, reviews displayed</t>
   </si>
   <si>
+    <t>Qty 2</t>
+  </si>
+  <si>
+    <t>Price recalculated correctly</t>
+  </si>
+  <si>
     <t>TC-0001</t>
   </si>
   <si>
@@ -156,6 +162,9 @@
   </si>
   <si>
     <t>TC-0010</t>
+  </si>
+  <si>
+    <t>TC-0019</t>
   </si>
   <si>
     <t>Registered user exists with valid 
@@ -179,9 +188,6 @@
     <t>Verify registration for new user with valid details</t>
   </si>
   <si>
-    <t>New user valid data (email,mobile number,otp)</t>
-  </si>
-  <si>
     <t>Signup successful,
 and move to secure home page</t>
   </si>
@@ -221,20 +227,12 @@
     <t>Function</t>
   </si>
   <si>
-    <t>Brand Name(like Reebok,Dot&amp;Key,Pume)</t>
-  </si>
-  <si>
     <t>Signup page accessible</t>
   </si>
   <si>
     <t>Verify search suggestion dropdown when hover on navigation listed keyword</t>
   </si>
   <si>
-    <t>Valid email/number
-(customer@gmail.com/
-9876543210)</t>
-  </si>
-  <si>
     <t>search bar</t>
   </si>
   <si>
@@ -244,67 +242,87 @@
     <t>Listed categorical Option viability</t>
   </si>
   <si>
-    <t>XYZ123ABC(invalid keywords or
-keyword that’s not available)</t>
+    <t>Login user &amp; Products available
+(PLP)</t>
+  </si>
+  <si>
+    <t>Product catalog available</t>
+  </si>
+  <si>
+    <t>Login -&gt;
+Hover on listed keyword -&gt; 
+Select</t>
+  </si>
+  <si>
+    <t>Login -&gt;
+Enter in search bar -&gt; 
+Press Enter</t>
+  </si>
+  <si>
+    <t>Login -&gt;
+Hover over brand Navigation key -&gt; 
+Select Brand name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Login -&gt;
+Click on any Product item-&gt;
+Open PDP </t>
+  </si>
+  <si>
+    <t>New user valid data (email, mobile number)</t>
+  </si>
+  <si>
+    <t>Brand Name</t>
+  </si>
+  <si>
+    <t>cart</t>
   </si>
   <si>
     <t>Goto https://www.purplle.com/&gt;
-Open sign in-&gt;
+Open login or register in-&gt;
 Enter credentials -&gt;
 Get Otp-&gt;
 Enter OTP</t>
   </si>
   <si>
     <t>Goto https://www.purplle.com/-&gt;
-Open sign in-&gt;
+Open login or register in-&gt;
 Enter credentials -&gt;
-clickGet Otp-&gt;/enter</t>
+click Get opt-&gt;/enter</t>
   </si>
   <si>
     <t>Goto https://www.purplle.com/ -&gt;
-Open sign in-&gt;
+Open login or register in-&gt;
 Enter credentials -&gt;
-Get Otp-&gt;
+Get opt-&gt;
 Enter OTP</t>
   </si>
   <si>
     <t>Goto https://www.purplle.com/-&gt;
-Open sign up-&gt;
+Open login or register in-&gt;
 Enter details -&gt;
 Get OTP -&gt; 
 Enter OTP</t>
   </si>
   <si>
-    <t>Login user &amp; Products available
-(PLP)</t>
-  </si>
-  <si>
-    <t>Product catalog available</t>
-  </si>
-  <si>
-    <t>Login -&gt;
-Enter in serch bar -&gt; 
-Press Enter</t>
-  </si>
-  <si>
-    <t>Login -&gt;
-Hover on listed keyword -&gt; 
-Select</t>
-  </si>
-  <si>
-    <t>Login -&gt;
-Enter in search bar -&gt; 
-Press Enter</t>
-  </si>
-  <si>
-    <t>Login -&gt;
-Hover over brand Navigation key -&gt; 
-Select Brand name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Login -&gt;
-Click on any Product item-&gt;
-Open PDP </t>
+    <t>Valid number
+(9876543210)</t>
+  </si>
+  <si>
+    <t>XYZ123ABC(OOPS! - Could not Find it)</t>
+  </si>
+  <si>
+    <t>Product in cart</t>
+  </si>
+  <si>
+    <t>Verify quantity increase in cart</t>
+  </si>
+  <si>
+    <t>Click on any Product item-&gt;
+Add to cart-&gt;
+Click on cart button-&gt;
+Click on quantity-&gt;
+Select dropdown(1,2,3,4,5)</t>
   </si>
 </sst>
 </file>
@@ -694,7 +712,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66E7AF51-FBF0-404C-8818-DC95D794B6CE}">
-  <dimension ref="A1:J34"/>
+  <dimension ref="A1:J35"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="33.54296875" customWidth="1"/>
@@ -743,7 +761,7 @@
     </row>
     <row r="2" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>9</v>
@@ -752,22 +770,22 @@
         <v>10</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>13</v>
@@ -775,31 +793,31 @@
     </row>
     <row r="3" spans="1:10" ht="58" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="J3" s="1" t="s">
         <v>13</v>
@@ -807,7 +825,7 @@
     </row>
     <row r="4" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>15</v>
@@ -816,7 +834,7 @@
         <v>10</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>16</v>
@@ -828,10 +846,10 @@
         <v>18</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J4" s="1" t="s">
         <v>13</v>
@@ -839,10 +857,10 @@
     </row>
     <row r="5" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>20</v>
@@ -854,16 +872,16 @@
         <v>12</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>45</v>
+        <v>71</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="J5" s="1" t="s">
         <v>13</v>
@@ -871,7 +889,7 @@
     </row>
     <row r="6" spans="1:10" ht="58" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>21</v>
@@ -886,16 +904,16 @@
         <v>12</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="J6" s="1" t="s">
         <v>13</v>
@@ -903,13 +921,13 @@
     </row>
     <row r="7" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>11</v>
@@ -918,13 +936,13 @@
         <v>12</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>64</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="I7" s="1" t="s">
         <v>23</v>
@@ -935,7 +953,7 @@
     </row>
     <row r="8" spans="1:10" ht="58" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>24</v>
@@ -953,13 +971,13 @@
         <v>62</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="J8" s="1" t="s">
         <v>19</v>
@@ -967,13 +985,13 @@
     </row>
     <row r="9" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>25</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>11</v>
@@ -982,30 +1000,30 @@
         <v>12</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="J9" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="59" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>26</v>
+        <v>81</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>27</v>
+        <v>73</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>11</v>
@@ -1014,32 +1032,52 @@
         <v>12</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>28</v>
+        <v>80</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J10" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
-      <c r="J11" s="1"/>
+    <row r="11" spans="1:10" ht="59" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12" s="1"/>
@@ -1317,6 +1355,18 @@
       <c r="I34" s="1"/>
       <c r="J34" s="1"/>
     </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A35" s="1"/>
+      <c r="B35" s="1"/>
+      <c r="C35" s="1"/>
+      <c r="D35" s="1"/>
+      <c r="E35" s="1"/>
+      <c r="F35" s="1"/>
+      <c r="G35" s="1"/>
+      <c r="H35" s="1"/>
+      <c r="I35" s="1"/>
+      <c r="J35" s="1"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
